--- a/artfynd/A 8314-2022 artfynd.xlsx
+++ b/artfynd/A 8314-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8314-2022 artfynd.xlsx
+++ b/artfynd/A 8314-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85396137</v>
+        <v>85396145</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>403901.7195254862</v>
+        <v>403902</v>
       </c>
       <c r="R2" t="n">
-        <v>6299437.773475694</v>
+        <v>6299438</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -760,19 +755,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -805,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85396172</v>
+        <v>85396122</v>
       </c>
       <c r="B3" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -857,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403861.2210658768</v>
+        <v>403893</v>
       </c>
       <c r="R3" t="n">
-        <v>6299441.442184926</v>
+        <v>6299459</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -890,19 +870,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -935,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>85396122</v>
+        <v>85396137</v>
       </c>
       <c r="B4" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +935,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403893.4278755553</v>
+        <v>403902</v>
       </c>
       <c r="R4" t="n">
-        <v>6299458.762150791</v>
+        <v>6299438</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1020,19 +985,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1065,15 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>85396145</v>
+        <v>85396172</v>
       </c>
       <c r="B5" t="n">
-        <v>95198</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,26 +1031,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>403901.7195254862</v>
+        <v>403861</v>
       </c>
       <c r="R5" t="n">
-        <v>6299437.773475694</v>
+        <v>6299441</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1150,19 +1100,9 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-05-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 8314-2022 artfynd.xlsx
+++ b/artfynd/A 8314-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85396145</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85396122</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85396137</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,8 +1152,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85396172</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>